--- a/data/credit_bond_2026-08-10.xlsx
+++ b/data/credit_bond_2026-08-10.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-10" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-11" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -37,6 +37,10 @@
       <sz val="12.0"/>
       <color indexed="8"/>
       <b val="true"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="12.0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -90,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
@@ -99,6 +103,12 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
       <protection locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -149,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY1"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -163,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-10</t>
+          <t>数据来源：DM    2026-08-11</t>
         </is>
       </c>
     </row>
@@ -668,6 +678,655 @@
           <t>团费(%)</t>
         </is>
       </c>
+    </row>
+    <row r="3" customHeight="true" ht="18.0">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>26金融街MTN004B</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>08-12 18:00</t>
+        </is>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>2.10 ~ 2.75</t>
+        </is>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>24金街06</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>2.95Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>2.7727</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>金融街控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>08-11 09:00</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>本期中期票据发行金额为20.80亿元,拟将募集资金全部用于偿还发行人债务融资工具的本金和利息或用于置换发行人已用于偿还债务融资工具利息的自有资金[23金融街MTN004A,23金融街MTN004B,23金融街MTN005]</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>平安证券股份有限公司,华夏银行股份有限公司,第一创业证券承销保荐有限责任公司</t>
+        </is>
+      </c>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>金融街控股股份有限公司2026年度第四期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>2031-08-13</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>住宅楼房</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>2029-08-13</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AY3" s="3"/>
+    </row>
+    <row r="4" customHeight="true" ht="18.0">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>26金融街MTN004A</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>08-12 18:00</t>
+        </is>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2+2</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2.00 ~ 2.65</t>
+        </is>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>23金融街MTN004B</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>1.98Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>2.5802</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>金融街控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>08-11 09:00</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>本期中期票据发行金额为20.80亿元,拟将募集资金全部用于偿还发行人债务融资工具的本金和利息或用于置换发行人已用于偿还债务融资工具利息的自有资金[23金融街MTN004A,23金融街MTN004B,23金融街MTN005]</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>平安证券股份有限公司,第一创业证券承销保荐有限责任公司,华夏银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>金融街控股股份有限公司2026年度第四期中期票据(品种一)</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>2030-08-13</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>住宅楼房</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>2028-08-13</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AY4" s="3"/>
+    </row>
+    <row r="5" customHeight="true" ht="18.0">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>26国耀03</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>08-11 18:00</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>245830.SH</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>25国耀融汇MTN002</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>2.10Y</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>1.9269</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>国耀融汇融资租赁有限公司</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>08-11 16:00</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于补充流动资金。根据公司财务状况和资金使用需求,公司未来可能调整部分流动资金用于偿还有息债务。</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,招商证券股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>国有企业</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>国耀融汇融资租赁有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>2028-08-13</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AY5" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-08-10.xlsx
+++ b/data/credit_bond_2026-08-10.xlsx
@@ -690,7 +690,11 @@
           <t>08-12 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>102683031.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -764,7 +768,11 @@
           <t>*</t>
         </is>
       </c>
-      <c r="W3" s="3"/>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>2.47%~2.57%</t>
+        </is>
+      </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -905,7 +913,11 @@
           <t>08-12 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>102683030.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>2+2</t>
@@ -979,7 +991,11 @@
           <t>*</t>
         </is>
       </c>
-      <c r="W4" s="3"/>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>2.34%~2.44%</t>
+        </is>
+      </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1198,7 +1214,11 @@
           <t>*</t>
         </is>
       </c>
-      <c r="W5" s="3"/>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>1.78%~1.88%</t>
+        </is>
+      </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
           <t>AAA</t>

--- a/data/credit_bond_2026-08-10.xlsx
+++ b/data/credit_bond_2026-08-10.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-11" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-12" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -173,252 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-11</t>
+          <t>数据来源：DM    2026-08-12</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>数据来源：DM    2026-08-12</t>
         </is>
       </c>
     </row>
@@ -510,170 +515,175 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
+          <t>最新边际</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
           <t>起息日</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>全场倍数</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>边际倍数</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>YY评分</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>标普信评PCA评分(主体)</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>yy定价</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>主体评级</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>债项评级</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>区域</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>募集资金用途</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>主承销商</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>担保人</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>债券类型</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>发行人类型</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AG2" s="2" t="inlineStr">
         <is>
           <t>交易市场</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AH2" s="2" t="inlineStr">
         <is>
           <t>债券全称</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>募集方式</t>
         </is>
       </c>
-      <c r="AI2" s="2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>实际到期日</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AK2" s="2" t="inlineStr">
         <is>
           <t>到期日休市情况</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr">
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>上市日</t>
         </is>
       </c>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>公告日</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="AN2" s="2" t="inlineStr">
         <is>
           <t>缴款日</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
+      <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>板块分类</t>
         </is>
       </c>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr">
         <is>
           <t>DM评分</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr">
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>DM一级行业</t>
         </is>
       </c>
-      <c r="AQ2" s="2" t="inlineStr">
+      <c r="AR2" s="2" t="inlineStr">
         <is>
           <t>DM二级行业</t>
         </is>
       </c>
-      <c r="AR2" s="2" t="inlineStr">
+      <c r="AS2" s="2" t="inlineStr">
         <is>
           <t>DM三级行业</t>
         </is>
       </c>
-      <c r="AS2" s="2" t="inlineStr">
+      <c r="AT2" s="2" t="inlineStr">
         <is>
           <t>申万行业</t>
         </is>
       </c>
-      <c r="AT2" s="2" t="inlineStr">
+      <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>行权日</t>
         </is>
       </c>
-      <c r="AU2" s="2" t="inlineStr">
+      <c r="AV2" s="2" t="inlineStr">
         <is>
           <t>是否有担保</t>
         </is>
       </c>
-      <c r="AV2" s="2" t="inlineStr">
+      <c r="AW2" s="2" t="inlineStr">
         <is>
           <t>条款</t>
         </is>
       </c>
-      <c r="AW2" s="2" t="inlineStr">
+      <c r="AX2" s="2" t="inlineStr">
         <is>
           <t>偿付顺序</t>
         </is>
       </c>
-      <c r="AX2" s="2" t="inlineStr">
+      <c r="AY2" s="2" t="inlineStr">
         <is>
           <t>发行截止日</t>
         </is>
       </c>
-      <c r="AY2" s="2" t="inlineStr">
+      <c r="AZ2" s="2" t="inlineStr">
         <is>
           <t>团费(%)</t>
         </is>
@@ -728,7 +738,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2.7727</t>
+          <t>2.7674</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -753,205 +763,214 @@
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="S3" s="3"/>
       <c r="T3" s="3"/>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="U3" s="3"/>
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>2.47%~2.57%</t>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>北京市</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>本期中期票据发行金额为20.80亿元,拟将募集资金全部用于偿还发行人债务融资工具的本金和利息或用于置换发行人已用于偿还债务融资工具利息的自有资金[23金融街MTN004A,23金融街MTN004B,23金融街MTN005]</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr">
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>平安证券股份有限公司,华夏银行股份有限公司,第一创业证券承销保荐有限责任公司</t>
         </is>
       </c>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3" t="inlineStr">
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
         </is>
       </c>
-      <c r="AE3" s="3" t="inlineStr">
+      <c r="AF3" s="3" t="inlineStr">
         <is>
           <t>地方国有企业</t>
         </is>
       </c>
-      <c r="AF3" s="3" t="inlineStr">
+      <c r="AG3" s="3" t="inlineStr">
         <is>
           <t>银行间</t>
         </is>
       </c>
-      <c r="AG3" s="3" t="inlineStr">
+      <c r="AH3" s="3" t="inlineStr">
         <is>
           <t>金融街控股股份有限公司2026年度第四期中期票据(品种二)</t>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
+      <c r="AI3" s="3" t="inlineStr">
         <is>
           <t>公募</t>
         </is>
       </c>
-      <c r="AI3" s="3" t="inlineStr">
+      <c r="AJ3" s="3" t="inlineStr">
         <is>
           <t>2031-08-13</t>
         </is>
       </c>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3" t="inlineStr">
+      <c r="AK3" s="3"/>
+      <c r="AL3" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="AL3" s="3" t="inlineStr">
+      <c r="AM3" s="3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AN3" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AO3" s="3" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
+      <c r="AQ3" s="3" t="inlineStr">
         <is>
           <t>房地产</t>
         </is>
       </c>
-      <c r="AQ3" s="3" t="inlineStr">
+      <c r="AR3" s="3" t="inlineStr">
         <is>
           <t>房地产开发</t>
         </is>
       </c>
-      <c r="AR3" s="3" t="inlineStr">
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <t>住宅楼房</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AT3" s="3" t="inlineStr">
         <is>
           <t>房地产开发</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
+      <c r="AU3" s="3" t="inlineStr">
         <is>
           <t>2029-08-13</t>
         </is>
       </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AV3" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>含权</t>
         </is>
       </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AX3" s="3" t="inlineStr">
         <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
+      <c r="AY3" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AY3" s="3"/>
+      <c r="AZ3" s="3"/>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN004A</t>
+          <t>26国耀03</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>08-12 18:00</t>
+          <t>08-11 19:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>102683030.IB</t>
+          <t>245830.SH</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2+2</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>10.4</v>
+        <v>7.0</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.65</t>
-        </is>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>54.72</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>23金融街MTN004B</t>
+          <t>25国耀融汇MTN002</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>1.98Y+2.00Y</t>
+          <t>2.10Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.5802</t>
+          <t>1.9269</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -961,7 +980,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司</t>
+          <t>国耀融汇融资租赁有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -971,210 +990,215 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>08-11 09:00</t>
+          <t>08-11 16:00</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="U4" s="3"/>
       <c r="V4" s="3" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
           <t>*</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>2.34%~2.44%</t>
-        </is>
-      </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
+          <t>1.78%~1.88%</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>北京市</t>
-        </is>
-      </c>
+      <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为20.80亿元,拟将募集资金全部用于偿还发行人债务融资工具的本金和利息或用于置换发行人已用于偿还债务融资工具利息的自有资金[23金融街MTN004A,23金融街MTN004B,23金融街MTN005]</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,第一创业证券承销保荐有限责任公司,华夏银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于补充流动资金。根据公司财务状况和资金使用需求,公司未来可能调整部分流动资金用于偿还有息债务。</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,招商证券股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第四期中期票据(品种一)</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
+          <t>国耀融汇融资租赁有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
           <t>公募</t>
         </is>
       </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>2030-08-13</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3"/>
+      <c r="AJ4" s="3" t="inlineStr">
+        <is>
+          <t>2028-08-13</t>
+        </is>
+      </c>
       <c r="AK4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL4" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
+      <c r="AN4" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>房地产</t>
-        </is>
-      </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>住宅楼房</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>2028-08-13</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>无担保</t>
         </is>
       </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
       <c r="AW4" s="3" t="inlineStr">
         <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AX4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AY4" s="3"/>
+      <c r="AY4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AZ4" s="3"/>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26国耀03</t>
+          <t>26金融街MTN004A</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>08-11 18:00</t>
+          <t>08-12 18:00</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>245830.SH</t>
+          <t>102683030.IB</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>7.0</v>
+        <v>10.4</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>2.00 ~ 2.65</t>
         </is>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>25国耀融汇MTN002</t>
+          <t>23金融街MTN004B</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.10Y</t>
+          <t>1.98Y+2.00Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.9269</t>
+          <t>2.5812</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1184,7 +1208,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>国耀融汇融资租赁有限公司</t>
+          <t>金融街控股股份有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -1194,163 +1218,168 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>08-11 16:00</t>
+          <t>08-11 09:00</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="S5" s="3"/>
       <c r="T5" s="3"/>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="U5" s="3"/>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>2.34%~2.44%</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>本期中期票据发行金额为20.80亿元,拟将募集资金全部用于偿还发行人债务融资工具的本金和利息或用于置换发行人已用于偿还债务融资工具利息的自有资金[23金融街MTN004A,23金融街MTN004B,23金融街MTN005]</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>平安证券股份有限公司,第一创业证券承销保荐有限责任公司,华夏银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>金融街控股股份有限公司2026年度第四期中期票据(品种一)</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr">
+        <is>
+          <t>2030-08-13</t>
+        </is>
+      </c>
+      <c r="AK5" s="3"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>1.78%~1.88%</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr">
-        <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于补充流动资金。根据公司财务状况和资金使用需求,公司未来可能调整部分流动资金用于偿还有息债务。</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="inlineStr">
-        <is>
-          <t>中信证券股份有限公司,招商证券股份有限公司,中国银河证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr">
-        <is>
-          <t>国有企业</t>
-        </is>
-      </c>
-      <c r="AF5" s="3" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="AG5" s="3" t="inlineStr">
-        <is>
-          <t>国耀融汇融资租赁有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
-        </is>
-      </c>
-      <c r="AH5" s="3" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="AI5" s="3" t="inlineStr">
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>住宅楼房</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
         <is>
           <t>2028-08-13</t>
         </is>
       </c>
-      <c r="AJ5" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="AK5" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AM5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AO5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AQ5" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AR5" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
+      <c r="AV5" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
         </is>
       </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AX5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AY5" s="3"/>
+      <c r="AY5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AZ5" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="B1:AY1"/>
+    <mergeCell ref="B1:AZ1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>

--- a/data/credit_bond_2026-08-10.xlsx
+++ b/data/credit_bond_2026-08-10.xlsx
@@ -713,7 +713,9 @@
       <c r="E3" s="4" t="n">
         <v>10.4</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>10.4</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>2.10 ~ 2.75</t>
@@ -1173,7 +1175,9 @@
       <c r="E5" s="4" t="n">
         <v>10.4</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4" t="n">
+        <v>10.4</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>2.00 ~ 2.65</t>

--- a/data/credit_bond_2026-08-10.xlsx
+++ b/data/credit_bond_2026-08-10.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-12" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-13" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-12</t>
+          <t>数据来源：DM    2026-08-13</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2.7674</t>
+          <t>2.7639</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">

--- a/data/credit_bond_2026-08-10.xlsx
+++ b/data/credit_bond_2026-08-10.xlsx
@@ -714,15 +714,19 @@
         <v>10.4</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10.4</v>
+        <v>10.0</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>2.10 ~ 2.75</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>127.27</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2.71</t>
@@ -773,8 +777,12 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
+      <c r="T3" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1176,15 +1184,19 @@
         <v>10.4</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>2.00 ~ 2.65</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>130.02</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>2.58</t>
@@ -1235,8 +1247,12 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
+      <c r="T5" s="4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>1.35</v>
+      </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
           <t>5</t>

--- a/data/credit_bond_2026-08-10.xlsx
+++ b/data/credit_bond_2026-08-10.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-13" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-14" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -173,257 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-13</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>数据来源：DM    2026-08-13</t>
+          <t>数据来源：DM    2026-08-14</t>
         </is>
       </c>
     </row>
@@ -540,150 +535,145 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>标普信评PCA评分(主体)</t>
+          <t>yy定价</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>yy定价</t>
+          <t>主体评级</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>主体评级</t>
+          <t>债项评级</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>债项评级</t>
+          <t>区域</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>区域</t>
+          <t>募集资金用途</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>募集资金用途</t>
+          <t>主承销商</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>主承销商</t>
+          <t>担保人</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>担保人</t>
+          <t>债券类型</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>债券类型</t>
+          <t>发行人类型</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>发行人类型</t>
+          <t>交易市场</t>
         </is>
       </c>
       <c r="AG2" s="2" t="inlineStr">
         <is>
-          <t>交易市场</t>
+          <t>债券全称</t>
         </is>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>债券全称</t>
+          <t>募集方式</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>募集方式</t>
+          <t>实际到期日</t>
         </is>
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>实际到期日</t>
+          <t>到期日休市情况</t>
         </is>
       </c>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>到期日休市情况</t>
+          <t>上市日</t>
         </is>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>上市日</t>
+          <t>公告日</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>公告日</t>
+          <t>缴款日</t>
         </is>
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>缴款日</t>
+          <t>板块分类</t>
         </is>
       </c>
       <c r="AO2" s="2" t="inlineStr">
         <is>
-          <t>板块分类</t>
+          <t>DM评分</t>
         </is>
       </c>
       <c r="AP2" s="2" t="inlineStr">
         <is>
-          <t>DM评分</t>
+          <t>DM一级行业</t>
         </is>
       </c>
       <c r="AQ2" s="2" t="inlineStr">
         <is>
-          <t>DM一级行业</t>
+          <t>DM二级行业</t>
         </is>
       </c>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>DM二级行业</t>
+          <t>DM三级行业</t>
         </is>
       </c>
       <c r="AS2" s="2" t="inlineStr">
         <is>
-          <t>DM三级行业</t>
+          <t>申万行业</t>
         </is>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>申万行业</t>
+          <t>行权日</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
         <is>
-          <t>行权日</t>
+          <t>是否有担保</t>
         </is>
       </c>
       <c r="AV2" s="2" t="inlineStr">
         <is>
-          <t>是否有担保</t>
+          <t>条款</t>
         </is>
       </c>
       <c r="AW2" s="2" t="inlineStr">
         <is>
-          <t>条款</t>
+          <t>偿付顺序</t>
         </is>
       </c>
       <c r="AX2" s="2" t="inlineStr">
         <is>
-          <t>偿付顺序</t>
+          <t>发行截止日</t>
         </is>
       </c>
       <c r="AY2" s="2" t="inlineStr">
-        <is>
-          <t>发行截止日</t>
-        </is>
-      </c>
-      <c r="AZ2" s="2" t="inlineStr">
         <is>
           <t>团费(%)</t>
         </is>
@@ -692,59 +682,59 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN004B</t>
+          <t>26国耀03</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>08-12 18:00</t>
+          <t>08-11 19:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>102683031.IB</t>
+          <t>245830.SH</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>10.4</v>
+        <v>7.0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2.10 ~ 2.75</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2.68</v>
+        <v>1.8</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>127.27</v>
+        <v>54.72</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>24金街06</t>
+          <t>25国耀融汇MTN002</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2.95Y+2.00Y</t>
+          <t>2.10Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2.7639</t>
+          <t>1.9269</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -754,7 +744,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司</t>
+          <t>国耀融汇融资租赁有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -764,7 +754,7 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>08-11 09:00</t>
+          <t>08-11 16:00</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
@@ -778,209 +768,204 @@
         </is>
       </c>
       <c r="T3" s="4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>2.63</v>
+      </c>
+      <c r="U3" s="3"/>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>2.47%~2.57%</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Y3" s="3"/>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于补充流动资金。根据公司财务状况和资金使用需求,公司未来可能调整部分流动资金用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为20.80亿元,拟将募集资金全部用于偿还发行人债务融资工具的本金和利息或用于置换发行人已用于偿还债务融资工具利息的自有资金[23金融街MTN004A,23金融街MTN004B,23金融街MTN005]</t>
-        </is>
-      </c>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>平安证券股份有限公司,华夏银行股份有限公司,第一创业证券承销保荐有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD3" s="3"/>
+          <t>中信证券股份有限公司,招商证券股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>国耀融汇融资租赁有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第四期中期票据(品种二)</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>2028-08-13</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2031-08-13</t>
-        </is>
-      </c>
-      <c r="AK3" s="3"/>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AN3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AP3" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AQ3" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>住宅楼房</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AT3" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t/>
         </is>
       </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
-          <t>2029-08-13</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AW3" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AX3" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AZ3" s="3"/>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AY3" s="3"/>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26国耀03</t>
+          <t>26金融街MTN004B</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>08-11 19:00</t>
+          <t>08-12 18:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>245830.SH</t>
+          <t>102683031.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F4" s="3"/>
+        <v>10.4</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>2.10 ~ 2.75</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.8</v>
+        <v>2.68</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>54.72</v>
+        <v>127.27</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>25国耀融汇MTN002</t>
+          <t>24金街06</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.10Y</t>
+          <t>2.95Y+2.00Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.9269</t>
+          <t>2.7639</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -990,7 +975,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>国耀融汇融资租赁有限公司</t>
+          <t>金融街控股股份有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -1000,7 +985,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>08-11 16:00</t>
+          <t>08-11 09:00</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -1013,151 +998,150 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
+      <c r="T4" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>2.47%~2.57%</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>本期中期票据发行金额为20.80亿元,拟将募集资金全部用于偿还发行人债务融资工具的本金和利息或用于置换发行人已用于偿还债务融资工具利息的自有资金[23金融街MTN004A,23金融街MTN004B,23金融街MTN005]</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>平安证券股份有限公司,华夏银行股份有限公司,第一创业证券承销保荐有限责任公司</t>
+        </is>
+      </c>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>金融街控股股份有限公司2026年度第四期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>2031-08-13</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>1.78%~1.88%</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于补充流动资金。根据公司财务状况和资金使用需求,公司未来可能调整部分流动资金用于偿还有息债务。</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>中信证券股份有限公司,招商证券股份有限公司,中国银河证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>国有企业</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>国耀融汇融资租赁有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>2028-08-13</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>住宅楼房</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>2029-08-13</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AW4" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AX4" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AZ4" s="3"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AY4" s="3"/>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
@@ -1248,7 +1232,7 @@
         </is>
       </c>
       <c r="T5" s="4" t="n">
-        <v>1.16</v>
+        <v>1.1574</v>
       </c>
       <c r="U5" s="4" t="n">
         <v>1.35</v>
@@ -1260,12 +1244,12 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>2.34%~2.44%</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>2.34%~2.44%</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1275,131 +1259,556 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>本期中期票据发行金额为20.80亿元,拟将募集资金全部用于偿还发行人债务融资工具的本金和利息或用于置换发行人已用于偿还债务融资工具利息的自有资金[23金融街MTN004A,23金融街MTN004B,23金融街MTN005]</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>平安证券股份有限公司,第一创业证券承销保荐有限责任公司,华夏银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>金融街控股股份有限公司2026年度第四期中期票据(品种一)</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>2030-08-13</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3"/>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>住宅楼房</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>2028-08-13</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AY5" s="3"/>
+    </row>
+    <row r="6" customHeight="true" ht="18.0">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>26北部湾银行01</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>08-14 16:00</t>
+        </is>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>1.40 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>25北部湾银行科创债</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>3.96Y</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>1.7007</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>广西北部湾银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>08-14 09:00</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="inlineStr">
-        <is>
-          <t>北京市</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="inlineStr">
-        <is>
-          <t>本期中期票据发行金额为20.80亿元,拟将募集资金全部用于偿还发行人债务融资工具的本金和利息或用于置换发行人已用于偿还债务融资工具利息的自有资金[23金融街MTN004A,23金融街MTN004B,23金融街MTN005]</t>
-        </is>
-      </c>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>平安证券股份有限公司,第一创业证券承销保荐有限责任公司,华夏银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="AF5" s="3" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>广西壮族自治区-南宁市</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>本期债券的募集资金将依据适用法律和主管部门的批准用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,兴业银行股份有限公司,国开证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <t>地方国有企业</t>
         </is>
       </c>
-      <c r="AG5" s="3" t="inlineStr">
+      <c r="AF6" s="3" t="inlineStr">
         <is>
           <t>银行间</t>
         </is>
       </c>
-      <c r="AH5" s="3" t="inlineStr">
-        <is>
-          <t>金融街控股股份有限公司2026年度第四期中期票据(品种一)</t>
-        </is>
-      </c>
-      <c r="AI5" s="3" t="inlineStr">
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>广西北部湾银行股份有限公司2026年金融债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
         <is>
           <t>公募</t>
         </is>
       </c>
-      <c r="AJ5" s="3" t="inlineStr">
-        <is>
-          <t>2030-08-13</t>
-        </is>
-      </c>
-      <c r="AK5" s="3"/>
-      <c r="AL5" s="3" t="inlineStr">
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>2029-08-18</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>城商行</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="AM5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AN5" s="3" t="inlineStr">
+      <c r="AY6" s="3"/>
+    </row>
+    <row r="7" customHeight="true" ht="18.0">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>26成都开投PPN002</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>08-14 18:00</t>
+        </is>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>5+5</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>成都经开国投集团有限公司</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>08-14 09:00</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>四川省-成都市</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>本期发行金额为2亿元,募集资金均用于偿还发行人存量债务融资工具本金。[23成都国投PPN002]</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>广发证券股份有限公司,国投证券股份有限公司,成都银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>成都经开国投集团有限公司2026年度第二期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>2036-08-17</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="AO5" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ5" s="3" t="inlineStr">
-        <is>
-          <t>房地产</t>
-        </is>
-      </c>
-      <c r="AR5" s="3" t="inlineStr">
-        <is>
-          <t>房地产开发</t>
-        </is>
-      </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>住宅楼房</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>房地产开发</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t>2028-08-13</t>
-        </is>
-      </c>
-      <c r="AV5" s="3" t="inlineStr">
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>2031-08-17</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
         </is>
       </c>
-      <c r="AW5" s="3" t="inlineStr">
+      <c r="AV7" s="3" t="inlineStr">
         <is>
           <t>含权</t>
         </is>
       </c>
-      <c r="AX5" s="3" t="inlineStr">
+      <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AY5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AZ5" s="3"/>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AY7" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="B1:AZ1"/>
+    <mergeCell ref="B1:AY1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>

--- a/data/credit_bond_2026-08-10.xlsx
+++ b/data/credit_bond_2026-08-10.xlsx
@@ -1406,7 +1406,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6800</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1629,19 +1629,27 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>26成都开投PPN001</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>4.94Y+5.00Y</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.1775</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.3000/2.1000</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -1676,7 +1684,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="W7" s="3"/>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>2.12%~2.22%</t>
+        </is>
+      </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
